--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/87.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/87.xlsx
@@ -426,13 +426,13 @@
         <v>-2.013351029819678</v>
       </c>
       <c r="E2">
-        <v>-13.01805611977166</v>
+        <v>-8.621759211437189</v>
       </c>
       <c r="F2">
-        <v>-4.22665452798508</v>
+        <v>-3.75868327438675</v>
       </c>
       <c r="G2">
-        <v>-9.851505691278136</v>
+        <v>-9.163712434095132</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.755939790056569</v>
       </c>
       <c r="E3">
-        <v>-13.5214412904643</v>
+        <v>-10.62599840859598</v>
       </c>
       <c r="F3">
-        <v>-4.156765170210885</v>
+        <v>-3.493109513416631</v>
       </c>
       <c r="G3">
-        <v>-9.86525400961221</v>
+        <v>-8.347036075278698</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.767929376241699</v>
       </c>
       <c r="E4">
-        <v>-13.98596309722311</v>
+        <v>-10.55926681561895</v>
       </c>
       <c r="F4">
-        <v>-3.615069217763399</v>
+        <v>-3.35359339033493</v>
       </c>
       <c r="G4">
-        <v>-9.312384582953571</v>
+        <v>-7.907765820229597</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.053875471414954</v>
       </c>
       <c r="E5">
-        <v>-15.10363576705623</v>
+        <v>-11.31112029816444</v>
       </c>
       <c r="F5">
-        <v>-3.68917993582226</v>
+        <v>-3.383647388075899</v>
       </c>
       <c r="G5">
-        <v>-9.643144841031837</v>
+        <v>-7.687838663986255</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.55149788235979</v>
       </c>
       <c r="E6">
-        <v>-14.93672527208152</v>
+        <v>-12.21919254855254</v>
       </c>
       <c r="F6">
-        <v>-3.334077054324974</v>
+        <v>-3.282623841467485</v>
       </c>
       <c r="G6">
-        <v>-9.641527198803031</v>
+        <v>-8.754130671715886</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.194827860513265</v>
       </c>
       <c r="E7">
-        <v>-15.62837722116904</v>
+        <v>-12.89078335778609</v>
       </c>
       <c r="F7">
-        <v>-2.953390873959627</v>
+        <v>-2.769546326051916</v>
       </c>
       <c r="G7">
-        <v>-9.640503457676484</v>
+        <v>-7.901269001541896</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.898982898052482</v>
       </c>
       <c r="E8">
-        <v>-16.00054985748943</v>
+        <v>-13.4111548344815</v>
       </c>
       <c r="F8">
-        <v>-2.422697297356124</v>
+        <v>-2.953036332711229</v>
       </c>
       <c r="G8">
-        <v>-10.34497188282459</v>
+        <v>-8.49410698801613</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.581932896538485</v>
       </c>
       <c r="E9">
-        <v>-17.07620734547939</v>
+        <v>-14.04122859401272</v>
       </c>
       <c r="F9">
-        <v>-2.343864885101306</v>
+        <v>-2.7222274949018</v>
       </c>
       <c r="G9">
-        <v>-9.761006319447091</v>
+        <v>-9.376922929806289</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.158076928343943</v>
       </c>
       <c r="E10">
-        <v>-17.60371116873688</v>
+        <v>-15.4374793993757</v>
       </c>
       <c r="F10">
-        <v>-2.172558506202368</v>
+        <v>-2.355689001408866</v>
       </c>
       <c r="G10">
-        <v>-10.41252567229043</v>
+        <v>-7.843893561353446</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.554230599846684</v>
       </c>
       <c r="E11">
-        <v>-18.3698701006726</v>
+        <v>-14.98515277311954</v>
       </c>
       <c r="F11">
-        <v>-1.977815128376024</v>
+        <v>-2.230793562986576</v>
       </c>
       <c r="G11">
-        <v>-9.759631487613683</v>
+        <v>-8.363593119267657</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.716654076777492</v>
       </c>
       <c r="E12">
-        <v>-19.26708759886431</v>
+        <v>-16.16104803326928</v>
       </c>
       <c r="F12">
-        <v>-1.236345951232395</v>
+        <v>-2.174342809587999</v>
       </c>
       <c r="G12">
-        <v>-9.504460730600346</v>
+        <v>-7.541499463656581</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.617795044718904</v>
       </c>
       <c r="E13">
-        <v>-19.03669695525008</v>
+        <v>-16.54043452868389</v>
       </c>
       <c r="F13">
-        <v>-1.303094139815174</v>
+        <v>-1.194045369808438</v>
       </c>
       <c r="G13">
-        <v>-8.814921863547719</v>
+        <v>-7.025278000595382</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.263926160794584</v>
       </c>
       <c r="E14">
-        <v>-19.73784058585768</v>
+        <v>-18.30945120046226</v>
       </c>
       <c r="F14">
-        <v>-1.000025985092141</v>
+        <v>-1.510348350525999</v>
       </c>
       <c r="G14">
-        <v>-8.417736556220055</v>
+        <v>-6.839186801073033</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.692042614896823</v>
       </c>
       <c r="E15">
-        <v>-20.94587895451386</v>
+        <v>-17.9439082500891</v>
       </c>
       <c r="F15">
-        <v>-0.4709361277804575</v>
+        <v>-1.827035693718458</v>
       </c>
       <c r="G15">
-        <v>-8.385403398973287</v>
+        <v>-6.177193789011944</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.9638546040908</v>
       </c>
       <c r="E16">
-        <v>-21.51398507572412</v>
+        <v>-18.514160867979</v>
       </c>
       <c r="F16">
-        <v>-0.4135890808520505</v>
+        <v>-1.032061437660606</v>
       </c>
       <c r="G16">
-        <v>-8.456494345280214</v>
+        <v>-6.437519345095168</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.155525968797867</v>
       </c>
       <c r="E17">
-        <v>-22.21844807777934</v>
+        <v>-20.19030306633406</v>
       </c>
       <c r="F17">
-        <v>-0.3729725703579851</v>
+        <v>-0.4864042322929327</v>
       </c>
       <c r="G17">
-        <v>-7.299243594701218</v>
+        <v>-5.236047571559534</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.340580601993781</v>
       </c>
       <c r="E18">
-        <v>-23.132756036876</v>
+        <v>-19.84965766605507</v>
       </c>
       <c r="F18">
-        <v>0.1092639982839554</v>
+        <v>-0.7624319898863812</v>
       </c>
       <c r="G18">
-        <v>-6.881206124363283</v>
+        <v>-4.999776650728599</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.585488030840887</v>
       </c>
       <c r="E19">
-        <v>-23.93894667903954</v>
+        <v>-22.41654617324489</v>
       </c>
       <c r="F19">
-        <v>0.1230546588057616</v>
+        <v>-0.6005043867219394</v>
       </c>
       <c r="G19">
-        <v>-6.399811546934029</v>
+        <v>-3.865599450155617</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.938560764537419</v>
       </c>
       <c r="E20">
-        <v>-25.22571256831907</v>
+        <v>-21.90745965377659</v>
       </c>
       <c r="F20">
-        <v>0.7600029221663575</v>
+        <v>-0.2701324140352321</v>
       </c>
       <c r="G20">
-        <v>-6.212591607195233</v>
+        <v>-4.339765496489413</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.426915181294207</v>
       </c>
       <c r="E21">
-        <v>-26.14057752971867</v>
+        <v>-22.89237557960085</v>
       </c>
       <c r="F21">
-        <v>0.9675851663686912</v>
+        <v>0.1445632184194508</v>
       </c>
       <c r="G21">
-        <v>-5.661533414837409</v>
+        <v>-3.765141570891657</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.06348958940374572</v>
       </c>
       <c r="E22">
-        <v>-25.65586778583367</v>
+        <v>-22.78243328764263</v>
       </c>
       <c r="F22">
-        <v>0.6594250372206499</v>
+        <v>0.2848025062437959</v>
       </c>
       <c r="G22">
-        <v>-5.737582286920659</v>
+        <v>-3.690447843312458</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.1595143301592159</v>
       </c>
       <c r="E23">
-        <v>-26.72573788404182</v>
+        <v>-23.88943234423967</v>
       </c>
       <c r="F23">
-        <v>0.8604590371038535</v>
+        <v>0.1974006332070172</v>
       </c>
       <c r="G23">
-        <v>-4.52279203507524</v>
+        <v>-3.054494605547121</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.2547694273025313</v>
       </c>
       <c r="E24">
-        <v>-27.5530357435551</v>
+        <v>-25.03444341165709</v>
       </c>
       <c r="F24">
-        <v>0.946407125348719</v>
+        <v>0.2173493770012349</v>
       </c>
       <c r="G24">
-        <v>-4.665407048934944</v>
+        <v>-3.160632279330479</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.2453108131563955</v>
       </c>
       <c r="E25">
-        <v>-27.33196017097464</v>
+        <v>-24.84222327545351</v>
       </c>
       <c r="F25">
-        <v>0.940466074335841</v>
+        <v>0.524733325892853</v>
       </c>
       <c r="G25">
-        <v>-4.012368490509579</v>
+        <v>-2.671159334421873</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.1600863469822852</v>
       </c>
       <c r="E26">
-        <v>-27.19409983675913</v>
+        <v>-25.13566386267654</v>
       </c>
       <c r="F26">
-        <v>0.9558322896577718</v>
+        <v>0.5666255221872297</v>
       </c>
       <c r="G26">
-        <v>-5.054008680663101</v>
+        <v>-2.29021935503502</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.02352205803629934</v>
       </c>
       <c r="E27">
-        <v>-27.83342074021402</v>
+        <v>-25.21861644954905</v>
       </c>
       <c r="F27">
-        <v>0.5323269698743162</v>
+        <v>0.2018199733009526</v>
       </c>
       <c r="G27">
-        <v>-4.695535225293766</v>
+        <v>-4.093460600129696</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.1383034709903073</v>
       </c>
       <c r="E28">
-        <v>-27.38550937611534</v>
+        <v>-25.01935453626354</v>
       </c>
       <c r="F28">
-        <v>0.4269660915448442</v>
+        <v>0.6666541995448811</v>
       </c>
       <c r="G28">
-        <v>-4.240242765369896</v>
+        <v>-3.867561620648165</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.3094509998300057</v>
       </c>
       <c r="E29">
-        <v>-27.62982054882916</v>
+        <v>-24.35409000521871</v>
       </c>
       <c r="F29">
-        <v>0.8061446432370956</v>
+        <v>0.5820604920035929</v>
       </c>
       <c r="G29">
-        <v>-4.529613694697325</v>
+        <v>-4.091006246403231</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.4789138918396209</v>
       </c>
       <c r="E30">
-        <v>-28.44970529639189</v>
+        <v>-24.37848036622402</v>
       </c>
       <c r="F30">
-        <v>0.4231141831218265</v>
+        <v>0.7794612724581178</v>
       </c>
       <c r="G30">
-        <v>-4.919045475480021</v>
+        <v>-4.566481500139246</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.6419947444881948</v>
       </c>
       <c r="E31">
-        <v>-26.94442242234623</v>
+        <v>-24.47665768271031</v>
       </c>
       <c r="F31">
-        <v>0.5689764288763747</v>
+        <v>0.2745589149407772</v>
       </c>
       <c r="G31">
-        <v>-4.976329041464806</v>
+        <v>-3.851654258527977</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8045794843753782</v>
       </c>
       <c r="E32">
-        <v>-27.45719964813077</v>
+        <v>-22.71013167163616</v>
       </c>
       <c r="F32">
-        <v>0.4358022866305066</v>
+        <v>0.07037629055953265</v>
       </c>
       <c r="G32">
-        <v>-5.43089307020248</v>
+        <v>-3.750303886999848</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.9732772050068969</v>
       </c>
       <c r="E33">
-        <v>-27.36928838221987</v>
+        <v>-23.97822666258207</v>
       </c>
       <c r="F33">
-        <v>0.5455559972970242</v>
+        <v>0.4229021210667098</v>
       </c>
       <c r="G33">
-        <v>-5.427900596140267</v>
+        <v>-4.040990586172615</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.160234744013443</v>
       </c>
       <c r="E34">
-        <v>-26.64468725625253</v>
+        <v>-23.03874944495077</v>
       </c>
       <c r="F34">
-        <v>0.7004532463139066</v>
+        <v>0.7652332339476335</v>
       </c>
       <c r="G34">
-        <v>-5.318878728606157</v>
+        <v>-4.822295376578234</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.377118706065413</v>
       </c>
       <c r="E35">
-        <v>-25.68005889398264</v>
+        <v>-24.00323289605242</v>
       </c>
       <c r="F35">
-        <v>0.4663135431778208</v>
+        <v>0.312359804632727</v>
       </c>
       <c r="G35">
-        <v>-5.999177675747389</v>
+        <v>-4.204247764862787</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.631685147447607</v>
       </c>
       <c r="E36">
-        <v>-26.4032607214816</v>
+        <v>-21.6216586022045</v>
       </c>
       <c r="F36">
-        <v>0.8050114366300658</v>
+        <v>0.4598539341707902</v>
       </c>
       <c r="G36">
-        <v>-6.07339234497891</v>
+        <v>-4.78397070876392</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.934114523394088</v>
       </c>
       <c r="E37">
-        <v>-25.34325363966216</v>
+        <v>-22.96282504973817</v>
       </c>
       <c r="F37">
-        <v>0.4067572403861475</v>
+        <v>0.4295158064106611</v>
       </c>
       <c r="G37">
-        <v>-6.129094362172044</v>
+        <v>-4.218964043556896</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.284890553165908</v>
       </c>
       <c r="E38">
-        <v>-24.9799568123968</v>
+        <v>-21.85484331428147</v>
       </c>
       <c r="F38">
-        <v>0.7294378217378613</v>
+        <v>0.4079210965870808</v>
       </c>
       <c r="G38">
-        <v>-6.20232794615729</v>
+        <v>-4.612835317109521</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.682349595891309</v>
       </c>
       <c r="E39">
-        <v>-24.77317310378455</v>
+        <v>-21.44716744174094</v>
       </c>
       <c r="F39">
-        <v>0.5994669762386189</v>
+        <v>0.4512231742010221</v>
       </c>
       <c r="G39">
-        <v>-6.368351194622074</v>
+        <v>-3.924064255901803</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.118129809906475</v>
       </c>
       <c r="E40">
-        <v>-24.24710480678749</v>
+        <v>-21.05493819404058</v>
       </c>
       <c r="F40">
-        <v>0.9142267084847638</v>
+        <v>0.7812240382912752</v>
       </c>
       <c r="G40">
-        <v>-6.502179097145586</v>
+        <v>-5.064098436958393</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.573767070385234</v>
       </c>
       <c r="E41">
-        <v>-24.20323295060118</v>
+        <v>-19.80212227439656</v>
       </c>
       <c r="F41">
-        <v>0.7626536978553159</v>
+        <v>0.3372472748824354</v>
       </c>
       <c r="G41">
-        <v>-6.26354241557029</v>
+        <v>-4.505263749504686</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.032598123191478</v>
       </c>
       <c r="E42">
-        <v>-22.93712143127064</v>
+        <v>-19.89250155864164</v>
       </c>
       <c r="F42">
-        <v>0.9663542124081311</v>
+        <v>0.6608282916009922</v>
       </c>
       <c r="G42">
-        <v>-6.505857346513723</v>
+        <v>-4.212470506090756</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.468738285091497</v>
       </c>
       <c r="E43">
-        <v>-23.30519127014008</v>
+        <v>-19.4544667963537</v>
       </c>
       <c r="F43">
-        <v>1.059586963593215</v>
+        <v>0.5673337763166233</v>
       </c>
       <c r="G43">
-        <v>-5.670422244041945</v>
+        <v>-4.316071795608662</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.86078384411914</v>
       </c>
       <c r="E44">
-        <v>-22.67594622135226</v>
+        <v>-17.67666941347445</v>
       </c>
       <c r="F44">
-        <v>0.8651625072169491</v>
+        <v>0.6734666930655043</v>
       </c>
       <c r="G44">
-        <v>-6.335289606189109</v>
+        <v>-3.481847463892319</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.192076866489975</v>
       </c>
       <c r="E45">
-        <v>-22.28887943402064</v>
+        <v>-18.28015197363263</v>
       </c>
       <c r="F45">
-        <v>1.094900265974558</v>
+        <v>0.8235105374693844</v>
       </c>
       <c r="G45">
-        <v>-6.058429974667842</v>
+        <v>-3.846903049709901</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.447895400927206</v>
       </c>
       <c r="E46">
-        <v>-21.22225625167599</v>
+        <v>-18.41244228481871</v>
       </c>
       <c r="F46">
-        <v>1.185444136570156</v>
+        <v>0.9174987597258218</v>
       </c>
       <c r="G46">
-        <v>-6.603526187452155</v>
+        <v>-4.468245007871031</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.628748545320297</v>
       </c>
       <c r="E47">
-        <v>-21.13957084476993</v>
+        <v>-18.02896657737518</v>
       </c>
       <c r="F47">
-        <v>1.261799730290603</v>
+        <v>1.084764362433904</v>
       </c>
       <c r="G47">
-        <v>-6.268638152652108</v>
+        <v>-3.797156449647159</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.735761448051314</v>
       </c>
       <c r="E48">
-        <v>-20.83588684934155</v>
+        <v>-16.45205230147619</v>
       </c>
       <c r="F48">
-        <v>0.8086678503460228</v>
+        <v>0.6870742843912918</v>
       </c>
       <c r="G48">
-        <v>-6.227987098752148</v>
+        <v>-4.287413606508473</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.779379477947677</v>
       </c>
       <c r="E49">
-        <v>-19.16943558536291</v>
+        <v>-17.55839020086811</v>
       </c>
       <c r="F49">
-        <v>0.9900885952331425</v>
+        <v>0.2456447507460604</v>
       </c>
       <c r="G49">
-        <v>-6.145346252555973</v>
+        <v>-4.865824061785828</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.775514822597244</v>
       </c>
       <c r="E50">
-        <v>-19.5842936176796</v>
+        <v>-15.13053037418779</v>
       </c>
       <c r="F50">
-        <v>0.9713509245818177</v>
+        <v>0.3474279102628413</v>
       </c>
       <c r="G50">
-        <v>-6.419364346206761</v>
+        <v>-4.026773053155541</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.735311081175534</v>
       </c>
       <c r="E51">
-        <v>-19.33108852201472</v>
+        <v>-14.18978971230835</v>
       </c>
       <c r="F51">
-        <v>0.5444302459966197</v>
+        <v>0.5418937850092477</v>
       </c>
       <c r="G51">
-        <v>-6.008299471682646</v>
+        <v>-4.282718178456907</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.678121733805755</v>
       </c>
       <c r="E52">
-        <v>-18.36679073834738</v>
+        <v>-14.24261436160783</v>
       </c>
       <c r="F52">
-        <v>0.6675687171575718</v>
+        <v>0.4551852554886122</v>
       </c>
       <c r="G52">
-        <v>-6.276001213831502</v>
+        <v>-4.264313806729982</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.612765323465118</v>
       </c>
       <c r="E53">
-        <v>-18.63751197147393</v>
+        <v>-15.51454044156422</v>
       </c>
       <c r="F53">
-        <v>0.9408868849764631</v>
+        <v>0.5626261643665137</v>
       </c>
       <c r="G53">
-        <v>-6.022119976891027</v>
+        <v>-4.350934774677763</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.546830478626279</v>
       </c>
       <c r="E54">
-        <v>-17.38037135915258</v>
+        <v>-14.08024592606281</v>
       </c>
       <c r="F54">
-        <v>0.4405057567436022</v>
+        <v>0.2833304973690212</v>
       </c>
       <c r="G54">
-        <v>-6.479610855259725</v>
+        <v>-4.655635571130918</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.487281445217779</v>
       </c>
       <c r="E55">
-        <v>-17.08643716826271</v>
+        <v>-13.05707798029576</v>
       </c>
       <c r="F55">
-        <v>0.5870522339728627</v>
+        <v>0.3446785588529497</v>
       </c>
       <c r="G55">
-        <v>-6.227193043134762</v>
+        <v>-4.463769421663947</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.429666126029637</v>
       </c>
       <c r="E56">
-        <v>-17.73300815860388</v>
+        <v>-14.11586690260714</v>
       </c>
       <c r="F56">
-        <v>0.3517834660667611</v>
+        <v>0.1870833172051494</v>
       </c>
       <c r="G56">
-        <v>-6.41836357363113</v>
+        <v>-4.07009502140489</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.378796166699918</v>
       </c>
       <c r="E57">
-        <v>-16.73492343036532</v>
+        <v>-13.11747423813606</v>
       </c>
       <c r="F57">
-        <v>0.2270363054095723</v>
+        <v>0.2815842988839198</v>
       </c>
       <c r="G57">
-        <v>-6.292062793364984</v>
+        <v>-4.761313873895954</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.330497265336479</v>
       </c>
       <c r="E58">
-        <v>-15.98513040349331</v>
+        <v>-12.96938408113722</v>
       </c>
       <c r="F58">
-        <v>0.3426258644288125</v>
+        <v>0.2115632306926804</v>
       </c>
       <c r="G58">
-        <v>-6.737193310119254</v>
+        <v>-4.506881391733492</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.281114817206363</v>
       </c>
       <c r="E59">
-        <v>-16.39469012122102</v>
+        <v>-11.37182902071127</v>
       </c>
       <c r="F59">
-        <v>0.4761719436385377</v>
+        <v>0.2994919453976395</v>
       </c>
       <c r="G59">
-        <v>-7.199005557281741</v>
+        <v>-5.21568759178318</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.230105233700109</v>
       </c>
       <c r="E60">
-        <v>-15.79156531050945</v>
+        <v>-12.29009939456465</v>
       </c>
       <c r="F60">
-        <v>0.3341591212047988</v>
+        <v>0.1621304059306199</v>
       </c>
       <c r="G60">
-        <v>-7.358837140663852</v>
+        <v>-5.13556016130154</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.167328384802982</v>
       </c>
       <c r="E61">
-        <v>-15.20082134773484</v>
+        <v>-11.33436948371982</v>
       </c>
       <c r="F61">
-        <v>0.4422337311458419</v>
+        <v>0.06267081697869165</v>
       </c>
       <c r="G61">
-        <v>-7.455088493888604</v>
+        <v>-4.635964647882047</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.093428561071241</v>
       </c>
       <c r="E62">
-        <v>-15.59837155239422</v>
+        <v>-11.69619908540669</v>
       </c>
       <c r="F62">
-        <v>0.2276608944312832</v>
+        <v>0.1285599885647671</v>
       </c>
       <c r="G62">
-        <v>-6.72427514083972</v>
+        <v>-5.772812762804417</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.00266732024665</v>
       </c>
       <c r="E63">
-        <v>-14.54105438413533</v>
+        <v>-12.19802646104069</v>
       </c>
       <c r="F63">
-        <v>-0.1829459165231814</v>
+        <v>-0.121886126895427</v>
       </c>
       <c r="G63">
-        <v>-7.360950247348135</v>
+        <v>-6.273382799027066</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.890468245637931</v>
       </c>
       <c r="E64">
-        <v>-15.1386861558756</v>
+        <v>-10.53882528394833</v>
       </c>
       <c r="F64">
-        <v>-0.2382775455605771</v>
+        <v>-0.03419515363507134</v>
       </c>
       <c r="G64">
-        <v>-7.603110960878274</v>
+        <v>-5.761121770388115</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.757266604170514</v>
       </c>
       <c r="E65">
-        <v>-14.99714870076586</v>
+        <v>-11.01148023002491</v>
       </c>
       <c r="F65">
-        <v>-0.05384320006207282</v>
+        <v>-0.2421476780664564</v>
       </c>
       <c r="G65">
-        <v>-7.642255934082449</v>
+        <v>-5.988674485535607</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.596417975686697</v>
       </c>
       <c r="E66">
-        <v>-14.82289754942471</v>
+        <v>-11.09058814246491</v>
       </c>
       <c r="F66">
-        <v>-0.07860807193616684</v>
+        <v>-0.3370868661013078</v>
       </c>
       <c r="G66">
-        <v>-7.478956099512005</v>
+        <v>-6.456232151648681</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.411807227241055</v>
       </c>
       <c r="E67">
-        <v>-13.94461360105907</v>
+        <v>-12.59722050176485</v>
       </c>
       <c r="F67">
-        <v>-0.2172452972034977</v>
+        <v>-0.1817812319548453</v>
       </c>
       <c r="G67">
-        <v>-7.864844161010501</v>
+        <v>-6.555033014025121</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.204119404358098</v>
       </c>
       <c r="E68">
-        <v>-14.77998572972803</v>
+        <v>-11.61817800672854</v>
       </c>
       <c r="F68">
-        <v>-0.2038655069134801</v>
+        <v>0.2963441492670014</v>
       </c>
       <c r="G68">
-        <v>-7.591157470737217</v>
+        <v>-6.232511903282622</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.97649954796008</v>
       </c>
       <c r="E69">
-        <v>-14.89205640446986</v>
+        <v>-10.44336052339263</v>
       </c>
       <c r="F69">
-        <v>-0.4565382739523993</v>
+        <v>-0.5340022232577922</v>
       </c>
       <c r="G69">
-        <v>-8.124211600398368</v>
+        <v>-6.309689515582321</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.739961191720531</v>
       </c>
       <c r="E70">
-        <v>-15.36241088575055</v>
+        <v>-10.27044074340973</v>
       </c>
       <c r="F70">
-        <v>-0.4090968444266688</v>
+        <v>-0.5669729026240182</v>
       </c>
       <c r="G70">
-        <v>-7.361327587827471</v>
+        <v>-6.045757897005267</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.500306517689373</v>
       </c>
       <c r="E71">
-        <v>-14.93853666168459</v>
+        <v>-10.85104092440716</v>
       </c>
       <c r="F71">
-        <v>-0.531007675096672</v>
+        <v>-0.2936704737857801</v>
       </c>
       <c r="G71">
-        <v>-7.623949999002307</v>
+        <v>-5.865927268218339</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.273172730010917</v>
       </c>
       <c r="E72">
-        <v>-14.25225548277016</v>
+        <v>-10.6303819714354</v>
       </c>
       <c r="F72">
-        <v>-0.4714695963878603</v>
+        <v>0.030901270346525</v>
       </c>
       <c r="G72">
-        <v>-7.529247382353614</v>
+        <v>-6.098372284710963</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.070874313614401</v>
       </c>
       <c r="E73">
-        <v>-14.00393661055955</v>
+        <v>-10.94227609023969</v>
       </c>
       <c r="F73">
-        <v>-0.139920513621775</v>
+        <v>-0.2719042919098203</v>
       </c>
       <c r="G73">
-        <v>-6.956526565260337</v>
+        <v>-6.076532474011298</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.903329885393239</v>
       </c>
       <c r="E74">
-        <v>-14.23847986483882</v>
+        <v>-10.742905493578</v>
       </c>
       <c r="F74">
-        <v>-0.5237718858332183</v>
+        <v>-0.2285856469478229</v>
       </c>
       <c r="G74">
-        <v>-6.949849279386866</v>
+        <v>-6.18524918794038</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.782532658089559</v>
       </c>
       <c r="E75">
-        <v>-15.04077149088175</v>
+        <v>-10.95782234150803</v>
       </c>
       <c r="F75">
-        <v>-0.5498613171843888</v>
+        <v>-0.2742634822729932</v>
       </c>
       <c r="G75">
-        <v>-7.166039124274</v>
+        <v>-6.502185659588704</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.707481081224785</v>
       </c>
       <c r="E76">
-        <v>-15.21660307965158</v>
+        <v>-11.56909840543341</v>
       </c>
       <c r="F76">
-        <v>-0.2923384590020785</v>
+        <v>-0.5795839679642378</v>
       </c>
       <c r="G76">
-        <v>-6.774963451490022</v>
+        <v>-5.366974874224497</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.67808322171703</v>
       </c>
       <c r="E77">
-        <v>-14.99741588073231</v>
+        <v>-11.01075567418368</v>
       </c>
       <c r="F77">
-        <v>-0.5909980424074123</v>
+        <v>-0.2357626221256778</v>
       </c>
       <c r="G77">
-        <v>-6.976381236916536</v>
+        <v>-5.130697390950443</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.686014194471404</v>
       </c>
       <c r="E78">
-        <v>-16.07705389737501</v>
+        <v>-12.04837398050921</v>
       </c>
       <c r="F78">
-        <v>-0.2178193558136378</v>
+        <v>-0.4514968299389615</v>
       </c>
       <c r="G78">
-        <v>-6.69485242711618</v>
+        <v>-4.948875060676933</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.717165671646379</v>
       </c>
       <c r="E79">
-        <v>-15.39019760226161</v>
+        <v>-12.17859477907378</v>
       </c>
       <c r="F79">
-        <v>-0.6106485739366221</v>
+        <v>-0.5334778666918202</v>
       </c>
       <c r="G79">
-        <v>-6.007764632568456</v>
+        <v>-4.504879846582231</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.760706255883682</v>
       </c>
       <c r="E80">
-        <v>-15.96887771027978</v>
+        <v>-13.24498700924404</v>
       </c>
       <c r="F80">
-        <v>-0.7792064297930711</v>
+        <v>-0.9729681922470979</v>
       </c>
       <c r="G80">
-        <v>-6.1820598405846</v>
+        <v>-5.081229694720254</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.799838664787338</v>
       </c>
       <c r="E81">
-        <v>-16.44564451075533</v>
+        <v>-13.25525758829344</v>
       </c>
       <c r="F81">
-        <v>-0.4099500628515523</v>
+        <v>-0.7113349750120964</v>
       </c>
       <c r="G81">
-        <v>-5.202674267078423</v>
+        <v>-4.099123988541297</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.824636856733212</v>
       </c>
       <c r="E82">
-        <v>-17.08073581948706</v>
+        <v>-13.57189754785776</v>
       </c>
       <c r="F82">
-        <v>-0.4570170703112174</v>
+        <v>-0.70475525273166</v>
       </c>
       <c r="G82">
-        <v>-5.381389280535138</v>
+        <v>-4.448623302945551</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.82643626156362</v>
       </c>
       <c r="E83">
-        <v>-17.31013472729361</v>
+        <v>-15.33295316233065</v>
       </c>
       <c r="F83">
-        <v>-0.6860333210609884</v>
+        <v>-0.4870221943754211</v>
       </c>
       <c r="G83">
-        <v>-5.218945844791708</v>
+        <v>-5.126553208120864</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.797567075580123</v>
       </c>
       <c r="E84">
-        <v>-19.27840425540948</v>
+        <v>-15.65093807867525</v>
       </c>
       <c r="F84">
-        <v>-0.7921422151551882</v>
+        <v>-0.7565447827546851</v>
       </c>
       <c r="G84">
-        <v>-5.386209395005962</v>
+        <v>-4.841753020425742</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.738517321026736</v>
       </c>
       <c r="E85">
-        <v>-19.21877330967648</v>
+        <v>-16.44163681125854</v>
       </c>
       <c r="F85">
-        <v>-0.8382218086707163</v>
+        <v>-1.022627161310123</v>
       </c>
       <c r="G85">
-        <v>-4.993312644256493</v>
+        <v>-3.991165236792447</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.648907232024855</v>
       </c>
       <c r="E86">
-        <v>-21.24216342341371</v>
+        <v>-17.1977198885272</v>
       </c>
       <c r="F86">
-        <v>-0.6388785066566265</v>
+        <v>-1.065395770316661</v>
       </c>
       <c r="G86">
-        <v>-5.045175632225076</v>
+        <v>-3.359805709210333</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.53583671821956</v>
       </c>
       <c r="E87">
-        <v>-20.95103235793459</v>
+        <v>-20.73782274470545</v>
       </c>
       <c r="F87">
-        <v>-0.7472753515173586</v>
+        <v>-0.5982835337150338</v>
       </c>
       <c r="G87">
-        <v>-4.661079117698037</v>
+        <v>-3.723958959099066</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.409666187246468</v>
       </c>
       <c r="E88">
-        <v>-22.18930734753998</v>
+        <v>-18.42548881843481</v>
       </c>
       <c r="F88">
-        <v>-0.6916836151154837</v>
+        <v>-0.6698287979274243</v>
       </c>
       <c r="G88">
-        <v>-5.117884220760812</v>
+        <v>-2.746948990001927</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.280445371759239</v>
       </c>
       <c r="E89">
-        <v>-23.21073183081408</v>
+        <v>-20.45352967497791</v>
       </c>
       <c r="F89">
-        <v>-0.7862342988384221</v>
+        <v>-1.019863727654383</v>
       </c>
       <c r="G89">
-        <v>-3.792146024325887</v>
+        <v>-4.241962125467045</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.165680530947441</v>
       </c>
       <c r="E90">
-        <v>-24.43796187231477</v>
+        <v>-22.57278758345753</v>
       </c>
       <c r="F90">
-        <v>-1.085897035168546</v>
+        <v>-1.244081246039737</v>
       </c>
       <c r="G90">
-        <v>-4.226126950221165</v>
+        <v>-3.976839423463912</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.077333196557777</v>
       </c>
       <c r="E91">
-        <v>-25.33584505618561</v>
+        <v>-23.67852772428044</v>
       </c>
       <c r="F91">
-        <v>-0.7353418907126289</v>
+        <v>-1.347938637533128</v>
       </c>
       <c r="G91">
-        <v>-4.379123749094952</v>
+        <v>-3.521697899731775</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.029077443308884</v>
       </c>
       <c r="E92">
-        <v>-27.32263604299285</v>
+        <v>-25.59641345058696</v>
       </c>
       <c r="F92">
-        <v>-1.039908562067326</v>
+        <v>-0.6084418031755642</v>
       </c>
       <c r="G92">
-        <v>-4.102352710555791</v>
+        <v>-2.841458014578613</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.031852374277404</v>
       </c>
       <c r="E93">
-        <v>-29.76295143743127</v>
+        <v>-28.15801722860982</v>
       </c>
       <c r="F93">
-        <v>-1.205755999781815</v>
+        <v>-1.026875857719081</v>
       </c>
       <c r="G93">
-        <v>-4.56060811354784</v>
+        <v>-3.467095091761056</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.088329006015309</v>
       </c>
       <c r="E94">
-        <v>-31.33284657861837</v>
+        <v>-29.38916440012715</v>
       </c>
       <c r="F94">
-        <v>-0.9497871588471565</v>
+        <v>-1.224398408181818</v>
       </c>
       <c r="G94">
-        <v>-4.242247591742716</v>
+        <v>-3.955170236285339</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.203442478618798</v>
       </c>
       <c r="E95">
-        <v>-32.98819628856721</v>
+        <v>-32.13192072387884</v>
       </c>
       <c r="F95">
-        <v>-0.9327335591257231</v>
+        <v>-1.58267807866884</v>
       </c>
       <c r="G95">
-        <v>-4.708876672154468</v>
+        <v>-3.813099905204501</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.372486828670592</v>
       </c>
       <c r="E96">
-        <v>-34.46025374881859</v>
+        <v>-33.52678581619548</v>
       </c>
       <c r="F96">
-        <v>-1.120931177735146</v>
+        <v>-1.213574959696839</v>
       </c>
       <c r="G96">
-        <v>-4.44496802212833</v>
+        <v>-4.119982713994688</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.585543488655064</v>
       </c>
       <c r="E97">
-        <v>-37.31996470652939</v>
+        <v>-36.57854029962355</v>
       </c>
       <c r="F97">
-        <v>-1.17296010593758</v>
+        <v>-1.48355812035206</v>
       </c>
       <c r="G97">
-        <v>-4.945567589345012</v>
+        <v>-4.162976560088091</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.834754774197283</v>
       </c>
       <c r="E98">
-        <v>-39.36419938612392</v>
+        <v>-37.59664541145003</v>
       </c>
       <c r="F98">
-        <v>-1.381088244258358</v>
+        <v>-1.134577702328865</v>
       </c>
       <c r="G98">
-        <v>-5.35396154951974</v>
+        <v>-3.629387591312751</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.094358950076539</v>
       </c>
       <c r="E99">
-        <v>-42.22944413907209</v>
+        <v>-41.10007894935116</v>
       </c>
       <c r="F99">
-        <v>-1.369751207983644</v>
+        <v>-1.729473066118941</v>
       </c>
       <c r="G99">
-        <v>-5.427995751565491</v>
+        <v>-4.635387152887585</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.361009303310468</v>
       </c>
       <c r="E100">
-        <v>-43.9180124701042</v>
+        <v>-42.92082211548215</v>
       </c>
       <c r="F100">
-        <v>-1.361273695983394</v>
+        <v>-1.605111096304054</v>
       </c>
       <c r="G100">
-        <v>-6.117528056175001</v>
+        <v>-4.529078855583135</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.602368651561969</v>
       </c>
       <c r="E101">
-        <v>-46.59134955155532</v>
+        <v>-46.65326511242519</v>
       </c>
       <c r="F101">
-        <v>-1.499201010386526</v>
+        <v>-1.52081477266037</v>
       </c>
       <c r="G101">
-        <v>-6.669183430856643</v>
+        <v>-5.254976938735971</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.833779315137459</v>
       </c>
       <c r="E102">
-        <v>-49.60665434769566</v>
+        <v>-47.94030271014518</v>
       </c>
       <c r="F102">
-        <v>-1.50979251599872</v>
+        <v>-1.27374011252957</v>
       </c>
       <c r="G102">
-        <v>-6.842897862656765</v>
+        <v>-5.337840907998188</v>
       </c>
     </row>
   </sheetData>
